--- a/artfynd/A 36808-2023 artfynd.xlsx
+++ b/artfynd/A 36808-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135593686</v>
       </c>
       <c r="B2" t="n">
-        <v>107650</v>
+        <v>107705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36808-2023 artfynd.xlsx
+++ b/artfynd/A 36808-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135593686</v>
       </c>
       <c r="B2" t="n">
-        <v>107705</v>
+        <v>107732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36808-2023 artfynd.xlsx
+++ b/artfynd/A 36808-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135593686</v>
       </c>
       <c r="B2" t="n">
-        <v>107737</v>
+        <v>107739</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36808-2023 artfynd.xlsx
+++ b/artfynd/A 36808-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135593686</v>
       </c>
       <c r="B2" t="n">
-        <v>107739</v>
+        <v>107762</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36808-2023 artfynd.xlsx
+++ b/artfynd/A 36808-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135593686</v>
       </c>
       <c r="B2" t="n">
-        <v>107762</v>
+        <v>107764</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36808-2023 artfynd.xlsx
+++ b/artfynd/A 36808-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135593686</v>
       </c>
       <c r="B2" t="n">
-        <v>107764</v>
+        <v>107765</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
